--- a/audits/jergens/jergens_audit.xlsx
+++ b/audits/jergens/jergens_audit.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -524,13 +524,13 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dimethicone [2,6] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Carbomer [1,4,6] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
+          <t>Dimethicone [2,6] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Carbomer [1,4,6] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Dilaurate, Hydrolyzed Silk</t>
+          <t>unknown — manual review needed: Stearic Acid, Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Arginine, Isopropyl Myristate, Sodium Hydroxide, Hydrolyzed Silk, Ananas Sativus (Pineapple) Fruit Juice, Citrus Grandis (Grapefruit) Juice, Citrus Limon (Lemon) Juice</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s), including Dimethicone, Mineral Oil, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 2 unknown ingredient(s) not in reference, see unknown column. 10 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, C12-15 Alkyl Benzoate, Arginine, Isopropyl Myristate, Sodium Hydroxide, Ananas Sativus (Pineapple) Fruit Juice, Citrus Grandis (Grapefruit) Juice, Citrus Limon (Lemon) Juice.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Arginine, Isopropyl Myristate, Sodium Hydroxide, Hydrolyzed Silk, Ananas Sativus (Pineapple) Fruit Juice, Citrus Grandis (Grapefruit) Juice, Citrus Limon (Lemon) Juice.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -582,36 +582,36 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avobenzone [2] / Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / Peg-100 Stearate [1,2,4,5] (inferred: PEG-) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Fragrance [1,2,4,8] / Propylparaben [2,4] / Laureth-7 [1,4,5] (inferred: -eth ethoxylate)</t>
+          <t>Avobenzone [2] / Octisalate [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / Peg-100 Stearate [1,2,4,5] (inferred: PEG-) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Fragrance [1,2,4,8] (fragrance without disclosure) / Propylparaben [2,4] / Laureth-7 [1,4,5] (inferred: -eth ethoxylate)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose</t>
+          <t>unknown — manual review needed: And Octocrylene, Dihydroxyacetone, Glyceryl Stearate, Phenyl Trimethicone, C12-15 Alkyl Benzoate, C13-14 Isoparaffin, Zea Mays (Corn) Starch, Tocopheryl Acetate, Caramel, Erythrulose</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, formaldehyde-releaser, heavy metals</t>
+          <t>heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13 flagged ingredient(s), including Avobenzone, Octisalate, Octocrylene. Escalation: PFAS, carcinogen in leave-on, formaldehyde-releaser, heavy metals.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 4 unknown ingredient(s) not in reference, see unknown column. 7 name(s) classified by template fallback (not in reference): Water, Glycerin, Glyceryl Stearate, C12-15 Alkyl Benzoate, Zea Mays (Corn) Starch, Tocopheryl Acetate, Caramel.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: And Octocrylene, Dihydroxyacetone, Glyceryl Stearate, Phenyl Trimethicone, C12-15 Alkyl Benzoate, C13-14 Isoparaffin, Zea Mays (Corn) Starch, Tocopheryl Acetate, Caramel, Erythrulose.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -656,28 +656,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Fragrance [1,2,4,8] / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Bht [1,2] (inferred: BHT) / Propylparaben [2,4] / Ethylparaben [2,4] / Butylene Glycol [1,2]</t>
+          <t>Petrolatum [1] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Fragrance [1,2,4,8] (fragrance without disclosure) / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Bht [1,2] / Propylparaben [2,4] / Ethylparaben [2,4] / Butylene Glycol [1,2]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Hydrolyzed Collagen, Polyimide-1, Hydrolyzed Elastin</t>
+          <t>unknown — manual review needed: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, formaldehyde-releaser</t>
+          <t>PFAS, formaldehyde-releaser, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s), including Petrolatum, Mineral Oil, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on, formaldehyde-releaser.</t>
+          <t>Ungradable: 18 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 7 unknown ingredient(s) not in reference, see unknown column. 13 name(s) classified by template fallback (not in reference): Water, Glycerin, Zea Mays (Corn) Starch, Stearic Acid, Isohexadecane, Polysorbate 60, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -722,11 +722,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fragrance [1,2,4,8] / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8]</t>
+          <t>Fragrance [1,2,4,8] (fragrance without disclosure) / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>PFAS, carcinogen in leave-on</t>
@@ -734,17 +738,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s), including Fragrance, Dimethicone, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 12 name(s) classified by template fallback (not in reference): Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -776,7 +780,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -784,28 +788,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dimethicone [2,6] / Aluminum Starch Octenylsuccinate [2,3] / Petrolatum [1] / Mineral Oil [1] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4] / Carbomer [1,4,6] / Propylene Glycol [1,2]</t>
+          <t>Dimethicone [2,6] / Aluminum Starch Octenylsuccinate [2,3] / Petrolatum [1] / Mineral Oil [1] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4] / Carbomer [1,4,6] / Propylene Glycol [1,2]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Dilaurate, Tridecyl Salicylate</t>
+          <t>unknown — manual review needed: Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Tridecyl Salicylate, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Citrus Aurantium Amara (Bitter Orange) Flower Extract, Honey Extract</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, heavy metals</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s), including Dimethicone, Aluminum Starch Octenylsuccinate, Petrolatum. Escalation: PFAS, carcinogen in leave-on, heavy metals.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 2 unknown ingredient(s) not in reference, see unknown column. 11 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Tapioca Starch, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Citrus Aurantium Amara (Bitter Orange) Flower Extract, Honey Extract.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Tridecyl Salicylate, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Citrus Aurantium Amara (Bitter Orange) Flower Extract, Honey Extract.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -842,7 +846,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -850,13 +854,13 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propanediol [4] / Ceteareth-25 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Geraniol [4,8] / Limonene [4,8] / Linalool [4,8] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / PEG-7 Trimethylolpropane Coconut Ether [1,2,4,5] (inferred: PEG-) / Coumarin [4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propanediol [4] / Ceteareth-25 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Geraniol [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag) / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / PEG-7 Trimethylolpropane Coconut Ether [1,2,4,5] (inferred: PEG-) / Coumarin [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext. Violet 2, Orange 4, Red 4, Yellow 10, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyisobutene</t>
+          <t>unknown — manual review needed: [Light Bronze shade] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Deep Bronze shade] Water, Zea Mays (Corn) Starch, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyisobutene, Tocopheryl Acetate, Sorbitan Isostearate, Caramel, Yellow 10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -866,12 +870,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14 flagged ingredient(s), including Alcohol Denat, Propanediol, Ceteareth-25. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 25 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 14. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Two shades (Light Bronze, Deep Bronze) each with its own ingredient list on the page; both captured and graded. Graded as one union across 2 shade/component lists. Fragrance listed; full flag applied. 16 unknown ingredient(s) not in reference, see unknown column. 9 name(s) classified by template fallback (not in reference): Water, Glycerin, Benzoic Acid, Zea Mays (Corn) Starch, Stearic Acid, Tocopheryl Acetate, Sorbitan Isostearate, Cocos Nucifera (Coconut) Oil, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Light Bronze shade] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Deep Bronze shade] Water, Zea Mays (Corn) Starch, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyisobutene, Tocopheryl Acetate, Sorbitan Isostearate, Caramel, Yellow 10.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -908,7 +912,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -916,29 +920,33 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Aluminum Starch Octenylsuccinate [2,3] / Dimethicone [2,6] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4] / Carbomer [1,4,6] / Pentylene Glycol [1,2] / Alcohol [4] (inferred: alcohol)</t>
+          <t>Petrolatum [1] / Aluminum Starch Octenylsuccinate [2,3] / Dimethicone [2,6] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4] / Carbomer [1,4,6] / Pentylene Glycol [1,2] / Alcohol [4] (inferred: alcohol)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Stearic Acid, C12-15 Alkyl Benzoate, Arginine, Sodium Hydroxide, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, heavy metals</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s), including Petrolatum, Aluminum Starch Octenylsuccinate, Dimethicone. Escalation: PFAS, carcinogen in leave-on, heavy metals.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 9 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, C12-15 Alkyl Benzoate, Arginine, Sodium Hydroxide, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, C12-15 Alkyl Benzoate, Arginine, Sodium Hydroxide, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -964,19 +972,26 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient list on page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Ingredients panel on the live page reads only the placeholder text NEED COPY. No INCI list is published on the page.</t>
+          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1013,7 +1028,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1021,13 +1036,13 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fragrance [1,2,4,8] / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Limonene [4,8]</t>
+          <t>Fragrance [1,2,4,8] (fragrance without disclosure) / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Benzyl Salicylate</t>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Benzyl Salicylate</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1037,12 +1052,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s), including Fragrance, Dimethicone, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 1 unknown ingredient(s) not in reference, see unknown column. 12 name(s) classified by template fallback (not in reference): Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Benzyl Salicylate.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1073,19 +1088,26 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient list on page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ingredients panel on the live page reads only the placeholder text NEED COPY. No INCI list is published on the page.</t>
+          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1122,7 +1144,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1130,13 +1152,13 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fragrance [1,2,4,8] / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Hydroxycitronellal [4,8] / Limonene [4,8]</t>
+          <t>Fragrance [1,2,4,8] (fragrance without disclosure) / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Hydroxycitronellal [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Citronellol</t>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1146,12 +1168,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s), including Fragrance, Dimethicone, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 1 unknown ingredient(s) not in reference, see unknown column. 12 name(s) classified by template fallback (not in reference): Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1188,7 +1210,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1196,13 +1218,13 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Mineral Oil [1] / Dimethicone [2,6] / Fragrance [1,2,4,8] / Carbomer [1,4,6] / Propylene Glycol [1,2] / Butylene Glycol [1,2] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
+          <t>Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Mineral Oil [1] / Dimethicone [2,6] / Fragrance [1,2,4,8] (fragrance without disclosure) / Carbomer [1,4,6] / Propylene Glycol [1,2] / Butylene Glycol [1,2] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Dilaurate</t>
+          <t>unknown — manual review needed: Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Stearic Acid, Isopropyl Myristate, Sodium Hydroxide, Arginine, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Cocos Nucifera (Coconut) Fruit Extract, Sorbitol</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1212,12 +1234,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s), including Ceteareth-20, Mineral Oil, Dimethicone. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 1 unknown ingredient(s) not in reference, see unknown column. 12 name(s) classified by template fallback (not in reference): Water, Glycerin, C12-15 Alkyl Benzoate, Stearic Acid, Isopropyl Myristate, Sodium Hydroxide, Arginine, Cocos Nucifera (Coconut) Oil, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Cocos Nucifera (Coconut) Fruit Extract, Sorbitol.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Stearic Acid, Isopropyl Myristate, Sodium Hydroxide, Arginine, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Cocos Nucifera (Coconut) Fruit Extract, Sorbitol.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1254,7 +1276,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1262,11 +1284,15 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Fragrance [1,2,4,8] / Propylene Glycol [1,2] / Butylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
+          <t>Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Fragrance [1,2,4,8] (fragrance without disclosure) / Propylene Glycol [1,2] / Butylene Glycol [1,2] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Stearic Acid, Hydrogenated Vegetable Oil, Isopropyl Myristate, Canola Oil, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Arginine, Sodium Hydroxide, Sodium Pca, Aloe Barbadensis Leaf Extract, Eucalyptus Globulus Leaf Extract, Cucumis Sativus (Cucumber) Fruit Extract</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>PFAS, carcinogen in leave-on</t>
@@ -1274,17 +1300,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s), including Ceteareth-20, Dimethicone, Fragrance. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 14 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Hydrogenated Vegetable Oil, Isopropyl Myristate, Canola Oil, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Arginine, Sodium Hydroxide, Sodium Pca, Aloe Barbadensis Leaf Extract, Eucalyptus Globulus Leaf Extract, Cucumis Sativus (Cucumber) Fruit Extract.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Hydrogenated Vegetable Oil, Isopropyl Myristate, Canola Oil, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Arginine, Sodium Hydroxide, Sodium Pca, Aloe Barbadensis Leaf Extract, Eucalyptus Globulus Leaf Extract, Cucumis Sativus (Cucumber) Fruit Extract.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1342,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1324,13 +1350,13 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Dimethicone [2,6] / Fragrance [1,2,4,8] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Dimethicone [2,6] / Fragrance [1,2,4,8] (fragrance without disclosure) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Dilaurate</t>
+          <t>unknown — manual review needed: Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1340,12 +1366,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s), including Alcohol Denat, Dimethicone, Fragrance. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 1 unknown ingredient(s) not in reference, see unknown column. 8 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1382,7 +1408,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1390,28 +1416,28 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Aluminum Starch Octenylsuccinate [2,3] / Cyclopentasiloxane [1,2,6] / Acrylates Copolymer [1,2,4,6] / Dimethicone [2,6] / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Fragrance [1,2,4,8] / Butylene Glycol [1,2] / Propylparaben [2,4]</t>
+          <t>Petrolatum [1] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Aluminum Starch Octenylsuccinate [2,3] / Cyclopentasiloxane [1,2,6] / Acrylates Copolymer [1,2,4,6] / Dimethicone [2,6] / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Fragrance [1,2,4,8] (fragrance without disclosure) / Butylene Glycol [1,2] / Propylparaben [2,4]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Dilaurate, Hydrolyzed Wheat Protein/Pvp Crosspolymer, Hydrolyzed Collagen, Polyimide-1, Hydrolyzed Elastin</t>
+          <t>unknown — manual review needed: Stearic Acid, Glyceryl Dilaurate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydrolyzed Wheat Protein/Pvp Crosspolymer, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Centella Asiatica Extract, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, formaldehyde-releaser, heavy metals</t>
+          <t>heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s), including Petrolatum, Mineral Oil, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on, formaldehyde-releaser, heavy metals.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 5 unknown ingredient(s) not in reference, see unknown column. 11 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Centella Asiatica Extract, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Fucus Vesiculosus Extract.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Glyceryl Dilaurate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydrolyzed Wheat Protein/Pvp Crosspolymer, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Centella Asiatica Extract, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1448,7 +1474,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1456,13 +1482,13 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fragrance [1,2,4,8] / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Geraniol [4,8] / Limonene [4,8] / Linalool [4,8]</t>
+          <t>Fragrance [1,2,4,8] (fragrance without disclosure) / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Geraniol [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Citronellol</t>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1472,12 +1498,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s), including Fragrance, Dimethicone, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 1 unknown ingredient(s) not in reference, see unknown column. 12 name(s) classified by template fallback (not in reference): Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1514,36 +1540,36 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Dimethicone [2,6] / Aluminum Starch Octenylsuccinate [2,3] / Mineral Oil [1] / Petrolatum [1] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Carbomer [1,4,6] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
+          <t>Alcohol [4] (inferred: alcohol) / Dimethicone [2,6] / Aluminum Starch Octenylsuccinate [2,3] / Mineral Oil [1] / Petrolatum [1] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Carbomer [1,4,6] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Dilaurate</t>
+          <t>unknown — manual review needed: Cetearyl, Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Persea Gratissima (Avocado) Oil, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, heavy metals</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s), including Dimethicone, Aluminum Starch Octenylsuccinate, Mineral Oil. Escalation: PFAS, carcinogen in leave-on, heavy metals.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 1 unknown ingredient(s) not in reference, see unknown column. 10 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Tapioca Starch, Sodium Hydroxide, Arginine, Persea Gratissima (Avocado) Oil, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Cetearyl, Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Persea Gratissima (Avocado) Oil, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1580,7 +1606,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1588,13 +1614,13 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Dimethicone [2,6] / Hydroxyethyl Urea [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Mineral Oil [1] / Fragrance [1,2,4,8] / Carbomer [1,4,6] / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Limonene [4,8]</t>
+          <t>Petrolatum [1] / Dimethicone [2,6] / Hydroxyethyl Urea [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Mineral Oil [1] / Fragrance [1,2,4,8] (fragrance without disclosure) / Carbomer [1,4,6] / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Anise Alcohol</t>
+          <t>unknown — manual review needed: Butyrospermum Parkii (Shea) Butter, Stearic Acid, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Hydroxyacetophenone, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butyrospermum Parkii (Shea) Oil, Tocopheryl Acetate, Anise Alcohol, Caramel</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1604,12 +1630,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s), including Petrolatum, Dimethicone, Hydroxyethyl Urea. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 16 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 4 unknown ingredient(s) not in reference, see unknown column. 14 name(s) classified by template fallback (not in reference): Water, Butyrospermum Parkii (Shea) Butter, Glycerin, Stearic Acid, Hydroxyacetophenone, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butyrospermum Parkii (Shea) Oil, Tocopheryl Acetate, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Stearic Acid, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Hydroxyacetophenone, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butyrospermum Parkii (Shea) Oil, Tocopheryl Acetate, Anise Alcohol, Caramel.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1646,7 +1672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1654,13 +1680,13 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Fragrance [1,2,4,8] / Dimethicone [2,6] / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Geraniol [4,8] / Limonene [4,8] / Linalool [4,8]</t>
+          <t>Fragrance [1,2,4,8] (fragrance without disclosure) / Dimethicone [2,6] / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Geraniol [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Agar, Glyceryl Dilaurate, Sodium Polyacrylate Starch, Citronellol, Ext. Violet 2</t>
+          <t>unknown — manual review needed: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1670,12 +1696,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s), including Fragrance, Dimethicone, 1,2-Hexanediol. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 5 unknown ingredient(s) not in reference, see unknown column. 10 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate.</t>
+          <t>Identical printed text on 1 other product(s): Lavender Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1712,7 +1738,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1724,25 +1750,29 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Stearic Acid, C12-15 Alkyl Benzoate, Caprylic/Capric Triglyceride, Hydroxyacetophenone, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, heavy metals</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s), including Petrolatum, Aluminum Starch Octenylsuccinate, Dimethicone. Escalation: PFAS, carcinogen in leave-on, heavy metals.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>12 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, C12-15 Alkyl Benzoate, Caprylic/Capric Triglyceride, Hydroxyacetophenone, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, C12-15 Alkyl Benzoate, Caprylic/Capric Triglyceride, Hydroxyacetophenone, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1768,19 +1798,26 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient list on page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>No ingredients section, INCI list, or fragrance disclosure appears anywhere on the live page (the Ingredients tab is absent).</t>
+          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1817,7 +1854,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1825,13 +1862,13 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fragrance [1,2,4,8] / Dimethicone [2,6] / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Geraniol [4,8] / Limonene [4,8] / Linalool [4,8]</t>
+          <t>Fragrance [1,2,4,8] (fragrance without disclosure) / Dimethicone [2,6] / 1,2-Hexanediol [1,2] / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Geraniol [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Agar, Glyceryl Dilaurate, Sodium Polyacrylate Starch, Citronellol, Ext. Violet 2</t>
+          <t>unknown — manual review needed: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1841,12 +1878,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s), including Fragrance, Dimethicone, 1,2-Hexanediol. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 5 unknown ingredient(s) not in reference, see unknown column. 10 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate.</t>
+          <t>Identical printed text on 1 other product(s): Sparkling Berry Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1883,7 +1920,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1891,13 +1928,13 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Dipropylene Glycol [2] / Dimethicone [2,6] / Polyquaternium-37 [2] (inferred: polyquaternium) / Fragrance [1,2,4,8] / PEG-2 Dimeadowfoamamidoethylmonium Methosulfate [1,2,4,5] (inferred: PEG-) / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethiconol [2,6] (inferred: silicone) / Hexylene Glycol [1,2] / PEG-45M [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Geraniol [4,8] / Limonene [4,8] / Linalool [4,8]</t>
+          <t>Mineral Oil [1] / Dipropylene Glycol [2] / Ethoxydiglycol [1,2] (inferred: -glycol) / Dimethicone [2,6] / Polyquaternium-37 [2] (inferred: -nium quat) / Fragrance [1,2,4,8] (fragrance without disclosure) / PEG-2 Dimeadowfoamamidoethylmonium Methosulfate [1,2,4,5] (inferred: PEG-) / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Hexylene Glycol [1,2] / PEG-45M [1,2,4,5] (inferred: PEG-) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Geraniol [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Isononanoate, Dihydroxyacetone, Ethylene/Propylene/Styrene Copolymer, Butylene/Ethylene/Styrene Copolymer, Erythrulose, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal</t>
+          <t>unknown — manual review needed: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Dihydroxyacetone, Isopropyl Palmitate, Ethylene/Propylene/Styrene Copolymer, Dimethiconol, Hydroxyacetophenone, Butylene/Ethylene/Styrene Copolymer, Tocopheryl Acetate, Erythrulose, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1907,12 +1944,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15 flagged ingredient(s), including Mineral Oil, Dipropylene Glycol, Dimethicone. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 15. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 9 unknown ingredient(s) not in reference, see unknown column. 8 name(s) classified by template fallback (not in reference): Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Isopropyl Palmitate, Ethoxydiglycol, Hydroxyacetophenone, Cocos Nucifera (Coconut) Oil, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Dihydroxyacetone, Isopropyl Palmitate, Ethylene/Propylene/Styrene Copolymer, Dimethiconol, Hydroxyacetophenone, Butylene/Ethylene/Styrene Copolymer, Tocopheryl Acetate, Erythrulose, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1949,21 +1986,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ALCOHOL DENAT [4] (inferred: alcohol denat) / CETEARETH-25 [1,4,5] (inferred: -eth ethoxylate) / METHYLPARABEN [2,4] / FRAGRANCE [1,2,4,8] / Dipropylene Glycol [2] / Linalool [4,8] / Propanediol [4] / Coumarin [4,8] / Geraniol [4,8] / Limonene [4,8]</t>
+          <t>ALCOHOL DENAT [4] (inferred: alcohol denat) / CETEARETH-25 [1,4,5] (inferred: -eth ethoxylate) / METHYLPARABEN [2,4] / FRAGRANCE [1,2,4,8] (fragrance without disclosure) / Dipropylene Glycol [2] / Ethoxydiglycol [1,2] (inferred: -glycol) / Propanediol [4] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Geraniol [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT. VIOLET 2, YELLOW 10, RED 4, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Dihydroxyacetone, Dimethyl Isosorbide, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Erythrulose, AlphaIsomethyl Ionone, Benzyl Salicylate, Citronellol, Ext. Violet 2, Orange 4, Red 4, Yellow 10, Cyclohexanol, 3-(5,5,6-trimethylbicyclo[2.2.1]hept-2-yl)-, (cis &amp; trans)-Tetrahydro-2-isobutyl-4-methylpyran-4-ol, gamma-Undecalactone, Hexamethylindanopyran, Benzyl Acetate</t>
+          <t>unknown — manual review needed: [Light Bronze Sunless Tanning Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Deep Bronze Sunless Tanning Mousse] WATER, Linalool || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Dimethyl Isosorbide, Benzoic Acid, AlphaIsomethyl Ionone, Benzyl Salicylate, Citronellol, Caramel, Red 4, Yellow 10 FRAGRANCE, Cyclohexanol, 3-(5,5,6-trimethylbicyclo[2.2.1]hept-2-yl), Tetrahydro-2-isobutyl-4-methylpyran-4-ol, gamma-Undecalactone, Hexamethylindanopyran, Benzyl Acetate</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1973,12 +2010,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s), including ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 28 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Bundle contains three sunless mousse shades (Light, Deep, Ultra Deep Bronze) and a Glow Body Applicator Mitt (fabric only: 100% Polyester, Made in UK). Mousse ingredient lists captured; mitt not an ingredient list. Shade lists are printed in upper case in the first two shades and mixed case in the third, reproduced as printed. Graded as one union across 3 shade/component lists. Fragrance listed; full flag applied. 27 unknown ingredient(s) not in reference, see unknown column. 7 name(s) classified by template fallback (not in reference): WATER, GLYCERIN, Water, Glycerin, Ethoxydiglycol, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Light Bronze Sunless Tanning Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Deep Bronze Sunless Tanning Mousse] WATER, Linalool || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Dimethyl Isosorbide, Benzoic Acid, AlphaIsomethyl Ionone, Benzyl Salicylate, Citronellol, Caramel, Red 4, Yellow 10 FRAGRANCE, Cyclohexanol, 3-(5,5,6-trimethylbicyclo[2.2.1]hept-2-yl), Tetrahydro-2-isobutyl-4-methylpyran-4-ol, gamma-Undecalactone, Hexamethylindanopyran, Benzyl Acetate.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2009,19 +2046,26 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient list on page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Accessory, not a cosmetic. Page lists fabric composition only ('Fabric: 100% Polyester. Made in UK.'). No INCI list.</t>
+          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2058,7 +2102,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2066,13 +2110,13 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propylene Glycol [1,2] / Propanediol [4] / Fragrance [1,2,4,8] / Phenoxyethanol [1,2,4,5,8] / Linalool [4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propylene Glycol [1,2] / Propanediol [4] / Fragrance [1,2,4,8] (fragrance without disclosure) / Phenoxyethanol [1,2,4,5,8] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Erythrulose, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal</t>
+          <t>unknown — manual review needed: Dihydroxyacetone, Polysorbate 20, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2082,12 +2126,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s), including Alcohol Denat, Propylene Glycol, Propanediol. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 5 unknown ingredient(s) not in reference, see unknown column. 7 name(s) classified by template fallback (not in reference): Water, Glycerin, Polysorbate 20, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Dihydroxyacetone, Polysorbate 20, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2124,7 +2168,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2138,7 +2182,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: DIHYDROXYACETONE, C13- 14 ISOPARAFFIN</t>
+          <t>unknown — manual review needed: ISOPROPYL PALMITATE, DIHYDROXYACETONE, ZEA MAYS (CORN) STARCH, SIMMONDSIA CHINENSIS (JOJOBA) SEED OIL, GLYCERYL STEARATE, HYDROXYPROPYL STARCH PHOSPHATE, BUTYROSPERMUM PARKII (SHEA) BUTTER, C13- 14 ISOPARAFFIN, TOCOPHERYL ACETATE, BENZOIC ACID</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,12 +2192,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s), including DIMETHICONE, LAURETH-3, PEG-100 STEARATE. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2 unknown ingredient(s) not in reference, see unknown column. 10 name(s) classified by template fallback (not in reference): WATER, GLYCERIN, ISOPROPYL PALMITATE, ZEA MAYS (CORN) STARCH, SIMMONDSIA CHINENSIS (JOJOBA) SEED OIL, GLYCERYL STEARATE, HYDROXYPROPYL STARCH PHOSPHATE, BUTYROSPERMUM PARKII (SHEA) BUTTER, TOCOPHERYL ACETATE, BENZOIC ACID.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: ISOPROPYL PALMITATE, DIHYDROXYACETONE, ZEA MAYS (CORN) STARCH, SIMMONDSIA CHINENSIS (JOJOBA) SEED OIL, GLYCERYL STEARATE, HYDROXYPROPYL STARCH PHOSPHATE, BUTYROSPERMUM PARKII (SHEA) BUTTER, C13- 14 ISOPARAFFIN, TOCOPHERYL ACETATE, BENZOIC ACID.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2190,36 +2234,36 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ALCOHOL DENAT [4] (inferred: alcohol denat) / CETEARETH-25 [1,4,5] (inferred: -eth ethoxylate) / METHYLPARABEN [2,4] / FRAGRANCE [1,2,4,8] / Dipropylene Glycol [2] / Linalool [4,8] / Avobenzone [2] / Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] (inferred: BHT)</t>
+          <t>ALCOHOL DENAT [4] (inferred: alcohol denat) / CETEARETH-25 [1,4,5] (inferred: -eth ethoxylate) / METHYLPARABEN [2,4] / FRAGRANCE [1,2,4,8] (fragrance without disclosure) / Dipropylene Glycol [2] / Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT. VIOLET 2, YELLOW 10, RED 4, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Dihydroxyacetone, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, (cis &amp; trans)-Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
+          <t>unknown — manual review needed: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, heavy metals</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23 flagged ingredient(s), including ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN. Escalation: PFAS, carcinogen in leave-on, heavy metals.</t>
+          <t>Ungradable: 44 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 22. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Bundle of three products (Instant Sun Mousse, Face Moisturizer Sunscreen, Daily Moisturizer). Each component's list captured in order. Components are shown in upper case as printed; the sunscreen and daily components include a separate FRAGRANCE INGREDIENTS line. Graded as one union across 3 shade/component lists. Fragrance listed; full flag applied. 26 unknown ingredient(s) not in reference, see unknown column. 22 name(s) classified by template fallback (not in reference): WATER, GLYCERIN, Water, Glycerin, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel, Isopropyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Cocos Nucifera (Coconut) Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2256,7 +2300,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2264,13 +2308,13 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propanediol [4] / Ceteareth-25 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Geraniol [4,8] / Limonene [4,8] / Linalool [4,8]</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propanediol [4] / Ceteareth-25 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Geraniol [4,8] (natural component, no source essential oil listed: full flag) / Limonene [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext. Violet 2, Orange 4, Red 4, Yellow 10</t>
+          <t>unknown — manual review needed: [Light Bronze Sunless Tanning Mousse] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Yellow 10</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2280,12 +2324,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s), including Alcohol Denat, Propanediol, Ceteareth-25. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 16 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Two shades on page (Light Bronze, Ultra Deep Bronze), each with its own list. Both graded. Graded as one union across 2 shade/component lists. Fragrance listed; full flag applied. 12 unknown ingredient(s) not in reference, see unknown column. 3 name(s) classified by template fallback (not in reference): Water, Glycerin, Benzoic Acid.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Light Bronze Sunless Tanning Mousse] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Yellow 10.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2322,7 +2366,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2330,11 +2374,15 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1] / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Steareth2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] / Linalool [4,8]</t>
+          <t>Petrolatum [1] / Mineral Oil [1] / Dimethicone [2,6] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Steareth2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Phenoxyethanol [1,2,4,5,8] / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Theobroma Cacao (Cocoa) Seed Butter, Stearic Acid, Hydrogenated Vegetable Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Butyrospermum Parkii (Shea) Butter, Jojoba Esters, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Caramel</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>PFAS, carcinogen in leave-on</t>
@@ -2342,17 +2390,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9 flagged ingredient(s), including Petrolatum, Mineral Oil, Dimethicone. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 13 name(s) classified by template fallback (not in reference): Water, Glycerin, Theobroma Cacao (Cocoa) Seed Butter, Stearic Acid, Hydrogenated Vegetable Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Butyrospermum Parkii (Shea) Butter, Jojoba Esters, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Theobroma Cacao (Cocoa) Seed Butter, Stearic Acid, Hydrogenated Vegetable Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Butyrospermum Parkii (Shea) Butter, Jojoba Esters, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Caramel.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2384,36 +2432,36 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Dimethicone [2,6] / Fragrance [1,2,4,8] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4] / Dipropylene Glycol [2] / Hydroxycitronellal [4,8] / Coumarin [4,8] / Phenethyl Alcohol [4,5,8] / Petrolatum [1] / Hydroxyethyl Urea [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Mineral Oil [1] / Carbomer [1,4,6] / Aluminum Starch Octenylsuccinate [2,3] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Propylparaben [2,4] / Pentylene Glycol [1,2] / Alcohol [4] (inferred: alcohol)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Dimethicone [2,6] / Fragrance [1,2,4,8] (fragrance without disclosure) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Dipropylene Glycol [2] / Hydroxycitronellal [4,8] (natural component, no source essential oil listed: full flag) / Coumarin [4,8] (natural component, no source essential oil listed: full flag) / Petrolatum [1] / Hydroxyethyl Urea [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Mineral Oil [1] / Carbomer [1,4,6] / Ethylparaben [2,4] / Aluminum Starch Octenylsuccinate [2,3] / Laureth-3 [1,4,5] (inferred: -eth ethoxylate) / Propylparaben [2,4] / Pentylene Glycol [1,2] / Alcohol [4] (inferred: alcohol)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glyceryl Dilaurate, Benzaldehyde, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Anisaldehyde</t>
+          <t>unknown — manual review needed: [Original Scent] Water, Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Ethylparaben With an illuminating HYDRALUCENCE™ blend and Cherry Almond Essence, Benzaldehyde, Phenethyl Alcohol || [Enriching Shea Butter] Water, Butyrospermum Parkii (Shea) Butter, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Caramel FRAGRANCE, Anisaldehyde || [Ultra Healing] Water, C12-15 Alkyl Benzoate, Lecithin, Ascorbyl Palmitate, Tocopherol FRAGRANCE</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, heavy metals</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>20 flagged ingredient(s), including Alcohol Denat, Dimethicone, Fragrance. Escalation: PFAS, carcinogen in leave-on, heavy metals.</t>
+          <t>Ungradable: 23 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 19. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Bundle of three products (Original Scent, Enriching Shea Butter, Ultra Healing). Each component's list captured in order. Graded as one union across 3 shade/component lists. Fragrance listed; full flag applied. 6 unknown ingredient(s) not in reference, see unknown column. 15 name(s) classified by template fallback (not in reference): Water, Glycerin, Stearic Acid, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Caramel, C12-15 Alkyl Benzoate, Lecithin, Ascorbyl Palmitate.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Original Scent] Water, Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Ethylparaben With an illuminating HYDRALUCENCE™ blend and Cherry Almond Essence, Benzaldehyde, Phenethyl Alcohol || [Enriching Shea Butter] Water, Butyrospermum Parkii (Shea) Butter, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Caramel FRAGRANCE, Anisaldehyde || [Ultra Healing] Water, C12-15 Alkyl Benzoate, Lecithin, Ascorbyl Palmitate, Tocopherol FRAGRANCE.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2450,7 +2498,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2458,13 +2506,13 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Petrolatum [1] / BHT [1,2] (inferred: BHT)</t>
+          <t>Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Petrolatum [1] / BHT [1,2]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Erythrulose</t>
+          <t>unknown — manual review needed: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2474,12 +2522,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s), including Mineral Oil, Propanediol, Ceteareth-20. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 5 unknown ingredient(s) not in reference, see unknown column. 15 name(s) classified by template fallback (not in reference): Water, Glycerin, Zea Mays (Corn) Starch, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Cocos Nucifera (Coconut) Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2510,19 +2558,26 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient list on page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>No ingredients tab or INCI list on the live page. Only marketing copy is printed.</t>
+          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2559,7 +2614,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2567,13 +2622,13 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Petrolatum [1] / Fragrance [1,2,4,8] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
+          <t>Mineral Oil [1] / Petrolatum [1] / Fragrance [1,2,4,8] (fragrance without disclosure) / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Butylene/Ethylene/Styrene Copolymer, Magnesium Aluminum Silicate</t>
+          <t>unknown — manual review needed: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/Styrene Copolymer, Magnesium Aluminum Silicate, Butyrospermum Parkii (Shea) Oil, Sodium Hydroxide, Tocopheryl Acetate, Caramel</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2583,12 +2638,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s), including Mineral Oil, Petrolatum, Fragrance. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 4 unknown ingredient(s) not in reference, see unknown column. 9 name(s) classified by template fallback (not in reference): Water, Glycerin, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butyrospermum Parkii (Shea) Oil, Sodium Hydroxide, Tocopheryl Acetate, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/Styrene Copolymer, Magnesium Aluminum Silicate, Butyrospermum Parkii (Shea) Oil, Sodium Hydroxide, Tocopheryl Acetate, Caramel.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2625,7 +2680,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2633,13 +2688,13 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
+          <t>Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Methylparaben [2,4] / Phenoxyethanol [1,2,4,5,8] / Ethylparaben [2,4]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Butylene/Ethylene/ Styrene Copolymer, Magnesium Aluminum Silicate</t>
+          <t>unknown — manual review needed: Ethylhexyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/ Styrene Copolymer, Magnesium Aluminum Silicate, Sodium Hydroxide</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2649,12 +2704,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s), including Mineral Oil, Ceteareth-20, Fragrance. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Fragrance listed; full flag applied. 4 unknown ingredient(s) not in reference, see unknown column. 5 name(s) classified by template fallback (not in reference): Water, Glycerin, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Cocos Nucifera (Coconut) Oil.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/ Styrene Copolymer, Magnesium Aluminum Silicate, Sodium Hydroxide.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2685,19 +2740,26 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient list on page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ingredients panel on the live page reads only the placeholder text NEED COPY. No INCI list is published, even though the product is marketed as fragrance free.</t>
+          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2734,36 +2796,36 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Avobenzone [2] / Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] (inferred: BHT) / Dipropylene Glycol [2] / Linalool [4,8]</t>
+          <t>Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] / Dipropylene Glycol [2] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, (cis &amp; trans)-Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
+          <t>unknown — manual review needed: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on, heavy metals</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>21 flagged ingredient(s), including Avobenzone, Octisalate, Octocrylene. Escalation: PFAS, carcinogen in leave-on, heavy metals.</t>
+          <t>Ungradable: 35 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 20. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Bundle of two products (Glow Face Moisturizer Sunscreen SPF 20, Glow Daily Moisturizer). Each list captured in order. Graded as one union across 2 shade/component lists. Fragrance listed; full flag applied. 16 unknown ingredient(s) not in reference, see unknown column. 20 name(s) classified by template fallback (not in reference): Water, Glycerin, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel, Isopropyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Cocos Nucifera (Coconut) Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2794,19 +2856,26 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient list on page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Digital gift card, not a cosmetic. No ingredient information on the page. Excluded from grading.</t>
+          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">

--- a/audits/jergens/jergens_audit.xlsx
+++ b/audits/jergens/jergens_audit.xlsx
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Arginine, Isopropyl Myristate, Sodium Hydroxide, Hydrolyzed Silk, Ananas Sativus (Pineapple) Fruit Juice, Citrus Grandis (Grapefruit) Juice, Citrus Limon (Lemon) Juice.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Arginine, Isopropyl Myristate, Sodium Hydroxide, Hydrolyzed Silk, Ananas Sativus (Pineapple) Fruit Juice, Citrus Grandis (Grapefruit) Juice, Citrus Limon (Lemon) Juice.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: And Octocrylene, Dihydroxyacetone, Glyceryl Stearate, Phenyl Trimethicone, C12-15 Alkyl Benzoate, C13-14 Isoparaffin, Zea Mays (Corn) Starch, Tocopheryl Acetate, Caramel, Erythrulose.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: And Octocrylene, Dihydroxyacetone, Glyceryl Stearate, Phenyl Trimethicone, C12-15 Alkyl Benzoate, C13-14 Isoparaffin, Zea Mays (Corn) Starch, Tocopheryl Acetate, Caramel, Erythrulose.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 18 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>Ungradable: 18 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Tridecyl Salicylate, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Citrus Aurantium Amara (Bitter Orange) Flower Extract, Honey Extract.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Tridecyl Salicylate, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Citrus Aurantium Amara (Bitter Orange) Flower Extract, Honey Extract.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 25 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 14. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 25 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 14. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Light Bronze shade] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Deep Bronze shade] Water, Zea Mays (Corn) Starch, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyisobutene, Tocopheryl Acetate, Sorbitan Isostearate, Caramel, Yellow 10.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Light Bronze shade] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Deep Bronze shade] Water, Zea Mays (Corn) Starch, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyisobutene, Tocopheryl Acetate, Sorbitan Isostearate, Caramel, Yellow 10.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, C12-15 Alkyl Benzoate, Arginine, Sodium Hydroxide, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, C12-15 Alkyl Benzoate, Arginine, Sodium Hydroxide, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Benzyl Salicylate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Benzyl Salicylate.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Stearic Acid, Isopropyl Myristate, Sodium Hydroxide, Arginine, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Cocos Nucifera (Coconut) Fruit Extract, Sorbitol.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Stearic Acid, Isopropyl Myristate, Sodium Hydroxide, Arginine, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Cocos Nucifera (Coconut) Fruit Extract, Sorbitol.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Hydrogenated Vegetable Oil, Isopropyl Myristate, Canola Oil, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Arginine, Sodium Hydroxide, Sodium Pca, Aloe Barbadensis Leaf Extract, Eucalyptus Globulus Leaf Extract, Cucumis Sativus (Cucumber) Fruit Extract.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Hydrogenated Vegetable Oil, Isopropyl Myristate, Canola Oil, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Arginine, Sodium Hydroxide, Sodium Pca, Aloe Barbadensis Leaf Extract, Eucalyptus Globulus Leaf Extract, Cucumis Sativus (Cucumber) Fruit Extract.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, Glyceryl Dilaurate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydrolyzed Wheat Protein/Pvp Crosspolymer, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Centella Asiatica Extract, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glyceryl Dilaurate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydrolyzed Wheat Protein/Pvp Crosspolymer, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Centella Asiatica Extract, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Cetearyl, Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Persea Gratissima (Avocado) Oil, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Cetearyl, Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Persea Gratissima (Avocado) Oil, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: 16 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butyrospermum Parkii (Shea) Butter, Stearic Acid, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Hydroxyacetophenone, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butyrospermum Parkii (Shea) Oil, Tocopheryl Acetate, Anise Alcohol, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Stearic Acid, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Hydroxyacetophenone, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butyrospermum Parkii (Shea) Oil, Tocopheryl Acetate, Anise Alcohol, Caramel.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Lavender Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
+          <t>Identical printed text on 1 other product(s): Lavender Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Stearic Acid, C12-15 Alkyl Benzoate, Caprylic/Capric Triglyceride, Hydroxyacetophenone, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, C12-15 Alkyl Benzoate, Caprylic/Capric Triglyceride, Hydroxyacetophenone, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Sparkling Berry Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
+          <t>Identical printed text on 1 other product(s): Sparkling Berry Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 15. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 15. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Dihydroxyacetone, Isopropyl Palmitate, Ethylene/Propylene/Styrene Copolymer, Dimethiconol, Hydroxyacetophenone, Butylene/Ethylene/Styrene Copolymer, Tocopheryl Acetate, Erythrulose, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Dihydroxyacetone, Isopropyl Palmitate, Ethylene/Propylene/Styrene Copolymer, Dimethiconol, Hydroxyacetophenone, Butylene/Ethylene/Styrene Copolymer, Tocopheryl Acetate, Erythrulose, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ungradable: 28 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 11. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 28 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Light Bronze Sunless Tanning Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Deep Bronze Sunless Tanning Mousse] WATER, Linalool || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Dimethyl Isosorbide, Benzoic Acid, AlphaIsomethyl Ionone, Benzyl Salicylate, Citronellol, Caramel, Red 4, Yellow 10 FRAGRANCE, Cyclohexanol, 3-(5,5,6-trimethylbicyclo[2.2.1]hept-2-yl), Tetrahydro-2-isobutyl-4-methylpyran-4-ol, gamma-Undecalactone, Hexamethylindanopyran, Benzyl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Light Bronze Sunless Tanning Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Deep Bronze Sunless Tanning Mousse] WATER, Linalool || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Dimethyl Isosorbide, Benzoic Acid, AlphaIsomethyl Ionone, Benzyl Salicylate, Citronellol, Caramel, Red 4, Yellow 10 FRAGRANCE, Cyclohexanol, 3-(5,5,6-trimethylbicyclo[2.2.1]hept-2-yl), Tetrahydro-2-isobutyl-4-methylpyran-4-ol, gamma-Undecalactone, Hexamethylindanopyran, Benzyl Acetate.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Dihydroxyacetone, Polysorbate 20, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Dihydroxyacetone, Polysorbate 20, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: ISOPROPYL PALMITATE, DIHYDROXYACETONE, ZEA MAYS (CORN) STARCH, SIMMONDSIA CHINENSIS (JOJOBA) SEED OIL, GLYCERYL STEARATE, HYDROXYPROPYL STARCH PHOSPHATE, BUTYROSPERMUM PARKII (SHEA) BUTTER, C13- 14 ISOPARAFFIN, TOCOPHERYL ACETATE, BENZOIC ACID.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: ISOPROPYL PALMITATE, DIHYDROXYACETONE, ZEA MAYS (CORN) STARCH, SIMMONDSIA CHINENSIS (JOJOBA) SEED OIL, GLYCERYL STEARATE, HYDROXYPROPYL STARCH PHOSPHATE, BUTYROSPERMUM PARKII (SHEA) BUTTER, C13- 14 ISOPARAFFIN, TOCOPHERYL ACETATE, BENZOIC ACID.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 44 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 22. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 44 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 22. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ungradable: 16 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Light Bronze Sunless Tanning Mousse] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Yellow 10.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Light Bronze Sunless Tanning Mousse] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Yellow 10.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Theobroma Cacao (Cocoa) Seed Butter, Stearic Acid, Hydrogenated Vegetable Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Butyrospermum Parkii (Shea) Butter, Jojoba Esters, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Theobroma Cacao (Cocoa) Seed Butter, Stearic Acid, Hydrogenated Vegetable Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Butyrospermum Parkii (Shea) Butter, Jojoba Esters, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Caramel.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 23 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 19. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 23 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 19. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Original Scent] Water, Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Ethylparaben With an illuminating HYDRALUCENCE™ blend and Cherry Almond Essence, Benzaldehyde, Phenethyl Alcohol || [Enriching Shea Butter] Water, Butyrospermum Parkii (Shea) Butter, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Caramel FRAGRANCE, Anisaldehyde || [Ultra Healing] Water, C12-15 Alkyl Benzoate, Lecithin, Ascorbyl Palmitate, Tocopherol FRAGRANCE.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Original Scent] Water, Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Ethylparaben With an illuminating HYDRALUCENCE™ blend and Cherry Almond Essence, Benzaldehyde, Phenethyl Alcohol || [Enriching Shea Butter] Water, Butyrospermum Parkii (Shea) Butter, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Caramel FRAGRANCE, Anisaldehyde || [Ultra Healing] Water, C12-15 Alkyl Benzoate, Lecithin, Ascorbyl Palmitate, Tocopherol FRAGRANCE.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/Styrene Copolymer, Magnesium Aluminum Silicate, Butyrospermum Parkii (Shea) Oil, Sodium Hydroxide, Tocopheryl Acetate, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/Styrene Copolymer, Magnesium Aluminum Silicate, Butyrospermum Parkii (Shea) Oil, Sodium Hydroxide, Tocopheryl Acetate, Caramel.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/ Styrene Copolymer, Magnesium Aluminum Silicate, Sodium Hydroxide.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/ Styrene Copolymer, Magnesium Aluminum Silicate, Sodium Hydroxide.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 35 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 20. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 35 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 20. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">

--- a/audits/jergens/jergens_audit.xlsx
+++ b/audits/jergens/jergens_audit.xlsx
@@ -652,17 +652,17 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Fragrance [1,2,4,8] (fragrance without disclosure) / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Bht [1,2] / Propylparaben [2,4] / Ethylparaben [2,4] / Butylene Glycol [1,2]</t>
+          <t>Petrolatum [1] / Mineral Oil [1] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Fragrance [1,2,4,8] (fragrance without disclosure) / Dmdm Hydantoin [1,2,4,5] / Methylparaben [2,4] / Bht [1,2] / Propylparaben [2,4] / Ethylparaben [2,4] / Polysorbate 60 [1,2,4,5] / Butylene Glycol [1,2]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel</t>
+          <t>unknown — manual review needed: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 18 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 13. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2106,17 +2106,17 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propylene Glycol [1,2] / Propanediol [4] / Fragrance [1,2,4,8] (fragrance without disclosure) / Phenoxyethanol [1,2,4,5,8] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
+          <t>Alcohol Denat [4] (inferred: alcohol denat) / Propylene Glycol [1,2] / Propanediol [4] / Polysorbate 20 [1,2,4,5] / Fragrance [1,2,4,8] (fragrance without disclosure) / Phenoxyethanol [1,2,4,5,8] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Dihydroxyacetone, Polysorbate 20, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel</t>
+          <t>unknown — manual review needed: Dihydroxyacetone, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Dihydroxyacetone, Polysorbate 20, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Dihydroxyacetone, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2238,17 +2238,17 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ALCOHOL DENAT [4] (inferred: alcohol denat) / CETEARETH-25 [1,4,5] (inferred: -eth ethoxylate) / METHYLPARABEN [2,4] / FRAGRANCE [1,2,4,8] (fragrance without disclosure) / Dipropylene Glycol [2] / Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
+          <t>ALCOHOL DENAT [4] (inferred: alcohol denat) / CETEARETH-25 [1,4,5] (inferred: -eth ethoxylate) / METHYLPARABEN [2,4] / FRAGRANCE [1,2,4,8] (fragrance without disclosure) / Dipropylene Glycol [2] / Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] / Polysorbate 60 [1,2,4,5] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
+          <t>unknown — manual review needed: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 44 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 22. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 43 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 23. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2502,17 +2502,17 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Petrolatum [1] / BHT [1,2]</t>
+          <t>Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Dimethicone [2,6] / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Petrolatum [1] / BHT [1,2] / Polysorbate 60 [1,2,4,5]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel</t>
+          <t>unknown — manual review needed: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2800,17 +2800,17 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] / Dipropylene Glycol [2] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
+          <t>Octisalate [2] / Octocrylene [2] / Aluminum Starch Octenylsuccinate [2,3] / Polyacrylamide [1] / Dimethicone [2,6] / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Diethylhexyl 2,6- Naphthalate [2] (inferred: phthalate) / Steareth-2 [1,4,5] (inferred: -eth ethoxylate) / Fragrance [1,2,4,8] (fragrance without disclosure) / Laureth-7 [1,4,5] (inferred: -eth ethoxylate) / Methylparaben [2,4] / Ethylparaben [2,4] / Propylparaben [2,4] / Mineral Oil [1] / Propanediol [4] / Ceteareth-20 [1,4,5] (inferred: -eth ethoxylate) / Petrolatum [1] / BHT [1,2] / Polysorbate 60 [1,2,4,5] / Dipropylene Glycol [2] / Linalool [4,8] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
+          <t>unknown — manual review needed: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 35 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 20. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 34 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 21. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Polysorbate 60, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">

--- a/audits/jergens/jergens_audit.xlsx
+++ b/audits/jergens/jergens_audit.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -540,17 +540,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Dimethicone, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Arginine, Isopropyl Myristate, Sodium Hydroxide, Hydrolyzed Silk, Ananas Sativus (Pineapple) Fruit Juice, Citrus Grandis (Grapefruit) Juice, Citrus Limon (Lemon) Juice.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -606,17 +606,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Avobenzone, Octisalate, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: And Octocrylene, Dihydroxyacetone, Glyceryl Stearate, Phenyl Trimethicone, C12-15 Alkyl Benzoate, C13-14 Isoparaffin, Zea Mays (Corn) Starch, Tocopheryl Acetate, Caramel, Erythrulose.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -672,17 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 17 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 13. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>13 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Centella Asiatica Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -738,17 +738,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Fragrance, Dimethicone, Ceteareth-20); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -804,17 +804,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Dimethicone, Aluminum Starch Octenylsuccinate, Petrolatum); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Tridecyl Salicylate, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Citrus Aurantium Amara (Bitter Orange) Flower Extract, Honey Extract.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -870,17 +870,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 25 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 14. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>14 flagged ingredient(s) in the printed list (Alcohol Denat, Propanediol, Ceteareth-25); tier applies to the printed subset only. 25 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Light Bronze shade] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Deep Bronze shade] Water, Zea Mays (Corn) Starch, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyisobutene, Tocopheryl Acetate, Sorbitan Isostearate, Caramel, Yellow 10.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 25 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -936,17 +936,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Petrolatum, Aluminum Starch Octenylsuccinate, Dimethicone); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, C12-15 Alkyl Benzoate, Arginine, Sodium Hydroxide, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Fragrance, Dimethicone, Ceteareth-20); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Benzyl Salicylate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Fragrance, Dimethicone, Ceteareth-20); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1234,17 +1234,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Ceteareth-20, Mineral Oil, Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Glyceryl Dilaurate, C12-15 Alkyl Benzoate, Stearic Acid, Isopropyl Myristate, Sodium Hydroxide, Arginine, Cocos Nucifera (Coconut) Water, Withania Somnifera Root Extract, Cocos Nucifera (Coconut) Fruit Extract, Sorbitol.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Ceteareth-20, Dimethicone, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Hydrogenated Vegetable Oil, Isopropyl Myristate, Canola Oil, Glyceryl Stearate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Arginine, Sodium Hydroxide, Sodium Pca, Aloe Barbadensis Leaf Extract, Eucalyptus Globulus Leaf Extract, Cucumis Sativus (Cucumber) Fruit Extract.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ungradable: 7 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Dimethicone, Fragrance); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1432,17 +1432,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 12. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, Glyceryl Dilaurate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydrolyzed Wheat Protein/Pvp Crosspolymer, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Centella Asiatica Extract, Cocos Nucifera (Coconut) Water, Hydrolyzed Collagen, Polyimide-1, Withania Somnifera Root Extract, Fucus Vesiculosus Extract, Hydrolyzed Elastin.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1498,17 +1498,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Fragrance, Dimethicone, Ceteareth-20); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Isopropyl Myristate, Simmondsia Chinensis (Jojoba) Seed Oil, Glyceryl Stearate, Hydroxyacetophenone, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tetrasodium Glutamate Diacetate, Sodium Hydroxide, Tocopheryl Acetate, Citronellol.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1564,17 +1564,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Alcohol, Dimethicone, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Cetearyl, Stearic Acid, Tapioca Starch, Glyceryl Dilaurate, Sodium Hydroxide, Arginine, Persea Gratissima (Avocado) Oil, Theobroma Cacao (Cocoa) Seed Butter, Tocopheryl Acetate, Butyrospermum Parkii (Shea) Butter.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1630,17 +1630,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 10. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Petrolatum, Dimethicone, Hydroxyethyl Urea); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butyrospermum Parkii (Shea) Butter, Stearic Acid, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Hydroxyacetophenone, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butyrospermum Parkii (Shea) Oil, Tocopheryl Acetate, Anise Alcohol, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Fragrance, Dimethicone, 1,2-Hexanediol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Lavender Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
+          <t>Identical printed text on 1 other product(s): Lavender Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1762,17 +1762,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Petrolatum, Aluminum Starch Octenylsuccinate, Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Stearic Acid, C12-15 Alkyl Benzoate, Caprylic/Capric Triglyceride, Hydroxyacetophenone, Arginine, Sodium Hydroxide, Tetrasodium Glutamate Diacetate, Argania Spinosa Kernel Oil, Lecithin, Ascorbyl Palmitate.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 8. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Fragrance, Dimethicone, 1,2-Hexanediol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Sparkling Berry Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Agar, Stearic Acid, Glyceryl Dilaurate, Hydroxyacetophenone, Sodium Polyacrylate Starch, Caprylic/Capric Triglyceride, Tetrasodium Glutamate Diacetate, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Citronellol, Ext, Violet 2.</t>
+          <t>Identical printed text on 1 other product(s): Sparkling Berry Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 15. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>15 flagged ingredient(s) in the printed list (Mineral Oil, Dipropylene Glycol, Ethoxydiglycol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Dihydroxyacetone, Isopropyl Palmitate, Ethylene/Propylene/Styrene Copolymer, Dimethiconol, Hydroxyacetophenone, Butylene/Ethylene/Styrene Copolymer, Tocopheryl Acetate, Erythrulose, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ungradable: 28 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 11. Escalation: carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN); tier applies to the printed subset only. 28 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Light Bronze Sunless Tanning Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Deep Bronze Sunless Tanning Mousse] WATER, Linalool || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Dimethyl Isosorbide, Benzoic Acid, AlphaIsomethyl Ionone, Benzyl Salicylate, Citronellol, Caramel, Red 4, Yellow 10 FRAGRANCE, Cyclohexanol, 3-(5,5,6-trimethylbicyclo[2.2.1]hept-2-yl), Tetrahydro-2-isobutyl-4-methylpyran-4-ol, gamma-Undecalactone, Hexamethylindanopyran, Benzyl Acetate.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 28 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Alcohol Denat, Propylene Glycol, Propanediol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Dihydroxyacetone, Erythrulose, Sodium Metabisulfite, Tocopheryl Acetate, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Hexyl Cinnamal, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 10 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (DIMETHICONE, LAURETH-3, PEG-100 STEARATE); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: ISOPROPYL PALMITATE, DIHYDROXYACETONE, ZEA MAYS (CORN) STARCH, SIMMONDSIA CHINENSIS (JOJOBA) SEED OIL, GLYCERYL STEARATE, HYDROXYPROPYL STARCH PHOSPHATE, BUTYROSPERMUM PARKII (SHEA) BUTTER, C13- 14 ISOPARAFFIN, TOCOPHERYL ACETATE, BENZOIC ACID.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2258,17 +2258,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 43 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 23. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>23 flagged ingredient(s) in the printed list (ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN); tier applies to the printed subset only. 43 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Instant Sun Moisturizing Mousse] WATER, DIHYDROXYACETONE, HYDROXYETHYL ACRYLATE/SODIUM ACRYLOYLDIMETHYL TAURATE COPOLYMER, ERYTHRULOSE, ORANGE 4, EXT, VIOLET 2, YELLOW 10, RED 4 FRAGRANCE, 4-tert-Butylcyclohexyl Acetate, Hexyl Cinnamal, Isocyclemone E, Linalool || [Glow Face Moisturizer Sunscreen] Avobenzone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Isohexadecane, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 43 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Alcohol Denat, Propanediol, Ceteareth-25); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Light Bronze Sunless Tanning Mousse] Water, Dihydroxyacetone, Erythrulose, Hydroxyethyl Acrylate/Sodium, Acryloyldimethyl Taurate Copolymer, Benzoic Acid, Alpha-Isomethyl Ionone, Benzyl Salicylate, Citronellol, Hexyl Cinnamal, Ext, Violet 2, Orange 4, Red 4, Yellow 10 || [Ultra Deep Bronze Sunless Tanning Mousse] Water, Yellow 10.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2390,17 +2390,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Dimethicone); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Theobroma Cacao (Cocoa) Seed Butter, Stearic Acid, Hydrogenated Vegetable Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Hydroxyacetophenone, Butyrospermum Parkii (Shea) Butter, Jojoba Esters, Sodium Hydroxide, Arginine, Tocopheryl Acetate, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 23 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 19. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>19 flagged ingredient(s) in the printed list (Alcohol Denat, Dimethicone, Fragrance); tier applies to the printed subset only. 23 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Original Scent] Water, Stearic Acid, Glyceryl Dilaurate, Lanolin Oil, Arginine, Sodium Hydroxide, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tocopheryl Acetate, Ethylparaben With an illuminating HYDRALUCENCE™ blend and Cherry Almond Essence, Benzaldehyde, Phenethyl Alcohol || [Enriching Shea Butter] Water, Butyrospermum Parkii (Shea) Butter, Octyldodecyl Myristate, Ethylhexyl Isononanoate, Hydrogenated Polydecene, Mangifera Indica (Mango) Seed Butter, Theobroma Cacao (Cocoa) Seed Butter, Caramel FRAGRANCE, Anisaldehyde || [Ultra Healing] Water, C12-15 Alkyl Benzoate, Lecithin, Ascorbyl Palmitate, Tocopherol FRAGRANCE.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 16 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 9. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>9 flagged ingredient(s) in the printed list (Mineral Oil, Propanediol, Ceteareth-20); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Zea Mays (Corn) Starch, Dihydroxyacetone, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Erythrulose, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2638,17 +2638,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Petrolatum, Fragrance); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Isononanoate, Butyrospermum Parkii (Shea) Butter, Theobroma Cacao (Cocoa) Seed Butter, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/Styrene Copolymer, Magnesium Aluminum Silicate, Butyrospermum Parkii (Shea) Oil, Sodium Hydroxide, Tocopheryl Acetate, Caramel.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ungradable: 6 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 6. Escalation: carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Mineral Oil, Ceteareth-20, Fragrance); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Butylene/Ethylene/ Styrene Copolymer, Magnesium Aluminum Silicate, Sodium Hydroxide.</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 34 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 21. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>21 flagged ingredient(s) in the printed list (Octisalate, Octocrylene, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 34 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: [Glow Face Moisturizer Sunscreen SPF 20] Avobenzone, Dihydroxyacetone, Dicaprylyl Ether, Glyceryl Stearate, C12-15 Alkyl Benzoate, Phenyl Trimethicone, C13-14 Isoparaffin, Erythrulose, Tocopheryl Acetate, Zea Mays (Corn) Starch, Caramel FRAGRANCE, Tetrahydro-2-isobutyl-4-methylpyran-4-ol, Methyldihydrojasmonate, Hexamethylindanopyran, Acetyl Hexamethyl Tetralin, Isopropyl Myristate || [Glow Daily Moisturizer] Water, Ethylhexyl Isononanoate, Octyldodecyl Myristate, Stearic Acid, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Isohexadecane, Olea Europaea (Olive) Fruit Oil, Avena Sativa (Oat) Meal Extract, Calendula Officinalis Flower Extract, Persea Gratissima (Avocado) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Camellia Sinensis Leaf Extract, Benzoic Acid, Isopropyl Myristate, Alpha-Isomethyl Ionone, Ethyl Linalool, Methyl Decenol, cis-3-Hexenyl Salicylate, 1-Trimethyl-2-Cyclohexenyl-1-Penten-3-One.</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 34 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">

--- a/audits/jergens/jergens_audit.xlsx
+++ b/audits/jergens/jergens_audit.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 25 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 25 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Lavender Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Identical printed text on 1 other product(s): Lavender Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Identical printed text on 1 other product(s): Sparkling Berry Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Identical printed text on 1 other product(s): Sparkling Berry Lotion Bursts. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 28 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 28 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 43 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 43 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 16 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 34 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 34 unknown ingredient(s) excluded from flags (2026-10-17).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">

--- a/audits/jergens/jergens_audit.xlsx
+++ b/audits/jergens/jergens_audit.xlsx
@@ -535,17 +535,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8 flagged ingredient(s) in the printed list (Dimethicone, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>8 flagged ingredient(s) in the printed list (Dimethicone, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s) in the printed list (Avobenzone, Octisalate, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Avobenzone, Octisalate, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Dmdm Hydantoin, Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PFAS, formaldehyde-releaser, carcinogen in leave-on</t>
+          <t>PFAS, formaldehyde-releaser, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>13 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 17 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, formaldehyde-releaser, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 17 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Dmdm Hydantoin, Methylparaben, Propylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (Dimethicone, Aluminum Starch Octenylsuccinate, Petrolatum); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Dimethicone, Aluminum Starch Octenylsuccinate, Petrolatum); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -931,17 +931,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s) in the printed list (Petrolatum, Aluminum Starch Octenylsuccinate, Dimethicone); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Petrolatum, Aluminum Starch Octenylsuccinate, Dimethicone); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1229,17 +1229,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10 flagged ingredient(s) in the printed list (Ceteareth-20, Mineral Oil, Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>10 flagged ingredient(s) in the printed list (Ceteareth-20, Mineral Oil, Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Ceteareth-20, Dimethicone, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Ceteareth-20, Dimethicone, Fragrance); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>PFAS, carcinogen in leave-on</t>
+          <t>PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Dimethicone, Fragrance); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Alcohol Denat, Dimethicone, Fragrance); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 7 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>12 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on.</t>
+          <t>12 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Ceteareth-20); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, formaldehyde-releaser, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Dmdm Hydantoin, Methylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (Alcohol, Dimethicone, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (Alcohol, Dimethicone, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 10 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>carcinogen in leave-on</t>
+          <t>carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11 flagged ingredient(s) in the printed list (ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN); tier applies to the printed subset only. 28 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>11 flagged ingredient(s) in the printed list (ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN); tier applies to the printed subset only. 28 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 28 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 28 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): METHYLPARABEN in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2253,17 +2253,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>23 flagged ingredient(s) in the printed list (ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN); tier applies to the printed subset only. 43 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>23 flagged ingredient(s) in the printed list (ALCOHOL DENAT, CETEARETH-25, METHYLPARABEN); tier applies to the printed subset only. 43 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 43 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 43 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): METHYLPARABEN, Methylparaben, Ethylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>19 flagged ingredient(s) in the printed list (Alcohol Denat, Dimethicone, Fragrance); tier applies to the printed subset only. 23 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>19 flagged ingredient(s) in the printed list (Alcohol Denat, Dimethicone, Fragrance); tier applies to the printed subset only. 23 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 23 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben With an illuminating HYDRALUCENCE™ blend and Cherry Almond Essence, Ethylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>carcinogen in leave-on</t>
+          <t>carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Petrolatum, Fragrance); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Mineral Oil, Petrolatum, Fragrance); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2699,17 +2699,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>carcinogen in leave-on</t>
+          <t>carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) in the printed list (Mineral Oil, Ceteareth-20, Fragrance); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
+          <t>6 flagged ingredient(s) in the printed list (Mineral Oil, Ceteareth-20, Fragrance); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 6 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>heavy metals, PFAS, carcinogen in leave-on</t>
+          <t>heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>21 flagged ingredient(s) in the printed list (Octisalate, Octocrylene, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 34 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on.</t>
+          <t>21 flagged ingredient(s) in the printed list (Octisalate, Octocrylene, Aluminum Starch Octenylsuccinate); tier applies to the printed subset only. 34 unknown ingredient(s) not in reference, excluded from grade. Escalation: heavy metals, PFAS, carcinogen in leave-on, paraben or DMDM hydantoin.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 34 unknown ingredient(s) excluded from flags (2026-10-17).</t>
+          <t>Heavy metal stacked with a cat. 1 or cat. 2 flag: Avoid (High Priority Swap). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 34 unknown ingredient(s) excluded from flags (2026-10-17). Practitioner rule (2026-10-17): Methylparaben, Ethylparaben, Propylparaben in the printed ingredient text: Avoid (High Priority Swap).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
